--- a/src/test/resources/teda/xlsx/LOAD_TEST.xlsx
+++ b/src/test/resources/teda/xlsx/LOAD_TEST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pad\Projects\teda-framework\src\test\resources\teda\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\teda-framework\src\test\resources\teda\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64DD24C-6A06-4C8B-8199-029C06292176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95617D58-891C-43CB-AFAB-64DD5B32C80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22640" yWindow="2880" windowWidth="25760" windowHeight="12940" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cockpit" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000000000"/>
-    <numFmt numFmtId="167" formatCode="#,##0.000000000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -138,17 +138,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -183,8 +186,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="C4:F5" totalsRowShown="0">
-  <autoFilter ref="C4:F5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="B3:E4" totalsRowShown="0">
+  <autoFilter ref="B3:E4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TRUNCATE"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="LOAD"/>
@@ -196,11 +199,11 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table13578" displayName="Table13578" ref="C4:F8" totalsRowShown="0">
-  <autoFilter ref="C4:F8" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table13578" displayName="Table13578" ref="B3:E7" totalsRowShown="0">
+  <autoFilter ref="B3:E7" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#ID" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="NAME" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#ID" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="NAME" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="AGE"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="AVERAGE"/>
   </tableColumns>
@@ -209,22 +212,22 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table4" displayName="Table4" ref="C4:F8">
-  <autoFilter ref="C4:F8" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table4" displayName="Table4" ref="B3:E7">
+  <autoFilter ref="B3:E7" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="#ID" totalsRowLabel="Ergebnis" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="NAME" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="#ID" totalsRowLabel="Ergebnis" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="NAME" dataDxfId="3"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="AGE"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="AVERAGE" totalsRowFunction="sum" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="AVERAGE" totalsRowFunction="sum" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -262,9 +265,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -297,26 +300,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -349,26 +335,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -545,57 +514,57 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="B3:F10"/>
+  <dimension ref="B2:E10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.1796875" customWidth="1"/>
     <col min="3" max="6" width="34.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B3" s="1" t="s">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
       <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E10" s="3"/>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -611,7 +580,7 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="B3:F19"/>
+  <dimension ref="B2:E19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="13.7265625" customWidth="1"/>
@@ -621,134 +590,129 @@
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B3" s="1" t="s">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C4" t="s">
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C5" s="2" t="s">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="D4">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>12.66</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5">
+        <v>45</v>
+      </c>
       <c r="E5">
-        <v>22</v>
-      </c>
-      <c r="F5">
-        <v>12.66</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>34.44</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>45</v>
-      </c>
-      <c r="F6">
-        <v>34.44</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>21</v>
-      </c>
-      <c r="F7">
         <v>24.33</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C8" s="2" t="s">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E8">
+      <c r="D7">
         <v>66</v>
       </c>
-      <c r="F8" s="7">
+      <c r="E7" s="5">
         <v>4.3939494940000001</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
     </row>
     <row r="18" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
     </row>
     <row r="19" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C3:E3"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -761,7 +725,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="B3:F9"/>
+  <dimension ref="B2:F9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.453125" customWidth="1"/>
@@ -771,88 +735,90 @@
     <col min="6" max="6" width="36.26953125" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+    </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C4" t="s">
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4">
+        <v>22</v>
+      </c>
+      <c r="E4" s="3">
+        <v>12.66</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5">
+        <v>45</v>
+      </c>
+      <c r="E5" s="3">
+        <v>34.44</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
         <v>21</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>22</v>
-      </c>
-      <c r="F5" s="4">
-        <v>12.66</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6">
-        <v>45</v>
-      </c>
-      <c r="F6" s="4">
-        <v>34.44</v>
+      <c r="E6" s="3">
+        <v>24.33</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>21</v>
-      </c>
-      <c r="F7" s="4">
-        <v>24.33</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C8" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E8">
+      <c r="D7">
         <v>66</v>
       </c>
-      <c r="F8" s="5">
+      <c r="E7" s="4">
         <v>4.3939494940000001</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="F9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
